--- a/StructureDefinition-mii-ex-prozedur-durchfuehrungsabsicht.xlsx
+++ b/StructureDefinition-mii-ex-prozedur-durchfuehrungsabsicht.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="144">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.0</t>
+    <t>2026.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-09</t>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,6 +90,9 @@
     <t>Purpose</t>
   </si>
   <si>
+    <t>Represent the intended purpose of a procedure.</t>
+  </si>
+  <si>
     <t>Copyright</t>
   </si>
   <si>
@@ -117,9 +123,6 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>Derivation</t>
   </si>
   <si>
@@ -238,9 +241,6 @@
   </si>
   <si>
     <t>Constraint(s)</t>
-  </si>
-  <si>
-    <t>Mapping: RIM Mapping</t>
   </si>
   <si>
     <t/>
@@ -283,9 +283,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Extension.extension</t>
   </si>
   <si>
@@ -325,9 +322,6 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Extension.value[x]</t>
   </si>
   <si>
@@ -394,9 +388,6 @@
     <t>Coding.system</t>
   </si>
   <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
     <t>Extension.value[x].version</t>
   </si>
   <si>
@@ -410,9 +401,6 @@
   </si>
   <si>
     <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
   </si>
   <si>
     <t>Extension.value[x].code</t>
@@ -434,9 +422,6 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>./code</t>
-  </si>
-  <si>
     <t>Extension.value[x].display</t>
   </si>
   <si>
@@ -450,9 +435,6 @@
   </si>
   <si>
     <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
   </si>
   <si>
     <t>Extension.value[x].userSelected</t>
@@ -475,9 +457,6 @@
   </si>
   <si>
     <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
   </si>
 </sst>
 </file>
@@ -670,114 +649,118 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -787,7 +770,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.30078125" customWidth="true" bestFit="true"/>
@@ -825,128 +808,124 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>74</v>
-      </c>
-      <c r="AK1" t="s" s="1">
         <v>75</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -975,7 +954,7 @@
         <v>9</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1026,7 +1005,7 @@
         <v>76</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>77</v>
@@ -1039,9 +1018,6 @@
       </c>
       <c r="AJ2" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>76</v>
       </c>
     </row>
     <row r="3">
@@ -1143,16 +1119,13 @@
       <c r="AJ3" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AK3" t="s" s="2">
-        <v>88</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1175,13 +1148,13 @@
         <v>76</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="L4" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1220,19 +1193,19 @@
         <v>76</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
@@ -1246,16 +1219,13 @@
       <c r="AJ4" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AK4" t="s" s="2">
-        <v>76</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1278,16 +1248,16 @@
         <v>76</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1337,7 +1307,7 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>83</v>
@@ -1350,17 +1320,14 @@
       </c>
       <c r="AJ5" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="AK5" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1383,13 +1350,13 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1416,11 +1383,11 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>76</v>
@@ -1438,7 +1405,7 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -1450,18 +1417,15 @@
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1555,20 +1519,17 @@
       <c r="AJ7" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AK7" t="s" s="2">
-        <v>88</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1587,16 +1548,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1634,19 +1595,19 @@
         <v>76</v>
       </c>
       <c r="AB8" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AC8" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="AC8" t="s" s="2">
+      <c r="AD8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE8" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="AD8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE8" t="s" s="2">
+      <c r="AF8" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -1660,16 +1621,13 @@
       <c r="AJ8" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AK8" t="s" s="2">
-        <v>88</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1689,29 +1647,29 @@
         <v>76</v>
       </c>
       <c r="J9" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="K9" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="O9" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O9" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="P9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>76</v>
@@ -1753,7 +1711,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -1765,18 +1723,15 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK9" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1796,19 +1751,19 @@
         <v>76</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -1858,7 +1813,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -1870,18 +1825,15 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK10" t="s" s="2">
-        <v>129</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1901,20 +1853,20 @@
         <v>76</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -1963,7 +1915,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -1975,18 +1927,15 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK11" t="s" s="2">
-        <v>136</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2006,20 +1955,20 @@
         <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K12" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -2068,7 +2017,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2080,18 +2029,15 @@
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>142</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2111,22 +2057,22 @@
         <v>76</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>76</v>
@@ -2175,7 +2121,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2187,10 +2133,7 @@
         <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>150</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-mii-ex-prozedur-durchfuehrungsabsicht.xlsx
+++ b/StructureDefinition-mii-ex-prozedur-durchfuehrungsabsicht.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-prozedur-durchfuehrungsabsicht.xlsx
+++ b/StructureDefinition-mii-ex-prozedur-durchfuehrungsabsicht.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
